--- a/Dynamic Data Sources for Power Query/Dynamische Databronnen voor Power Query (NL).xlsx
+++ b/Dynamic Data Sources for Power Query/Dynamische Databronnen voor Power Query (NL).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgoos\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E6D71F-F87E-4AF8-8662-108A1E4CE304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DB79E3-9982-4DDD-8E4D-C7D633F0B32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E1A5ED9-1123-42E8-9B91-2AFAA7DA74F0}"/>
   </bookViews>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="55">
   <si>
     <t>Regio</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>2026-Q3</t>
+  </si>
+  <si>
+    <t>27-09-2026</t>
   </si>
 </sst>
 </file>
@@ -463,7 +466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -515,6 +518,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -531,55 +537,55 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1142,22 +1148,22 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C629FA6-09A3-4C7B-9515-2CF915542811}" name="Demo_CSV" displayName="Demo_CSV" ref="A1:P51" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:P51" xr:uid="{6C629FA6-09A3-4C7B-9515-2CF915542811}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{FEED0FFB-34E6-43B7-BE1E-5C6CB8E7F40E}" uniqueName="1" name="Project_ID" queryTableFieldId="1" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{95D4F798-D440-4434-B0FF-D71B6081E3A7}" uniqueName="2" name="Projectnaam" queryTableFieldId="2" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{992B01C4-B1A0-430C-8D41-B0687A931213}" uniqueName="3" name="Categorie" queryTableFieldId="3" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{8DD50EFE-0A9E-4B20-80C3-2C0C6F5D4449}" uniqueName="4" name="Afdeling" queryTableFieldId="4" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{F70254B0-129C-482E-A442-6ABD37C55200}" uniqueName="5" name="Projectleider" queryTableFieldId="5" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{E19BC787-F754-45BB-9B0D-E800317B8F5A}" uniqueName="6" name="Opdrachtgever" queryTableFieldId="6" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{7E1313A5-9EF6-4A74-A8B7-4ADB98D7A0F9}" uniqueName="7" name="Prioriteit" queryTableFieldId="7" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{11AB329E-2552-4F1E-AF7B-965CA738DC01}" uniqueName="8" name="Status" queryTableFieldId="8" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{57E6EFC5-3E51-4CA8-999D-907B33F7A7EA}" uniqueName="9" name="Startdatum" queryTableFieldId="9" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{AAB42422-E2C6-40F3-98D1-D47D061F6522}" uniqueName="10" name="Einddatum_gepland" queryTableFieldId="10" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{F7A8C4D0-5031-4E2A-9F30-7675F9CBF935}" uniqueName="11" name="Einddatum_werkelijk" queryTableFieldId="11" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{FEED0FFB-34E6-43B7-BE1E-5C6CB8E7F40E}" uniqueName="1" name="Project_ID" queryTableFieldId="1" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{95D4F798-D440-4434-B0FF-D71B6081E3A7}" uniqueName="2" name="Projectnaam" queryTableFieldId="2" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{992B01C4-B1A0-430C-8D41-B0687A931213}" uniqueName="3" name="Categorie" queryTableFieldId="3" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{8DD50EFE-0A9E-4B20-80C3-2C0C6F5D4449}" uniqueName="4" name="Afdeling" queryTableFieldId="4" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{F70254B0-129C-482E-A442-6ABD37C55200}" uniqueName="5" name="Projectleider" queryTableFieldId="5" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{E19BC787-F754-45BB-9B0D-E800317B8F5A}" uniqueName="6" name="Opdrachtgever" queryTableFieldId="6" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{7E1313A5-9EF6-4A74-A8B7-4ADB98D7A0F9}" uniqueName="7" name="Prioriteit" queryTableFieldId="7" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{11AB329E-2552-4F1E-AF7B-965CA738DC01}" uniqueName="8" name="Status" queryTableFieldId="8" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{57E6EFC5-3E51-4CA8-999D-907B33F7A7EA}" uniqueName="9" name="Startdatum" queryTableFieldId="9" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{AAB42422-E2C6-40F3-98D1-D47D061F6522}" uniqueName="10" name="Einddatum_gepland" queryTableFieldId="10" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{F7A8C4D0-5031-4E2A-9F30-7675F9CBF935}" uniqueName="11" name="Einddatum_werkelijk" queryTableFieldId="11" dataDxfId="17"/>
     <tableColumn id="12" xr3:uid="{3739D346-F6CA-4A7E-91FC-8EEEC9F000FF}" uniqueName="12" name="Voortgang_pct" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{F9E0DC93-D8FA-4078-A5A8-AF1A242311BF}" uniqueName="13" name="Budget_EUR" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{D22E5635-4089-4D7D-9F21-4D47BB49B911}" uniqueName="14" name="Kosten_EUR" queryTableFieldId="14"/>
-    <tableColumn id="15" xr3:uid="{47082C6B-DA44-47B0-B6E5-7B3335F50164}" uniqueName="15" name="Risico" queryTableFieldId="15" dataDxfId="1"/>
-    <tableColumn id="16" xr3:uid="{D0960E6C-2C86-4E9F-9EDB-C96E40D07CB5}" uniqueName="16" name="Regio" queryTableFieldId="16" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{47082C6B-DA44-47B0-B6E5-7B3335F50164}" uniqueName="15" name="Risico" queryTableFieldId="15" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{D0960E6C-2C86-4E9F-9EDB-C96E40D07CB5}" uniqueName="16" name="Regio" queryTableFieldId="16" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1192,22 +1198,22 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{DDAE2E8D-C7FF-490D-B63F-EED3D8F8F6F6}" name="Demo_XLS" displayName="Demo_XLS" ref="A1:P51" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:P51" xr:uid="{DDAE2E8D-C7FF-490D-B63F-EED3D8F8F6F6}"/>
   <tableColumns count="16">
-    <tableColumn id="17" xr3:uid="{0253E53A-40A2-4DC8-A9DD-E43E7FA56125}" uniqueName="17" name="Project_ID" queryTableFieldId="17" dataDxfId="27"/>
-    <tableColumn id="18" xr3:uid="{CC51713D-8C64-4013-8757-A5457F2FE0D9}" uniqueName="18" name="Projectnaam" queryTableFieldId="18" dataDxfId="26"/>
-    <tableColumn id="19" xr3:uid="{A1C2B82E-44B8-4820-A84A-0772B352AB67}" uniqueName="19" name="Categorie" queryTableFieldId="19" dataDxfId="25"/>
-    <tableColumn id="20" xr3:uid="{BDAC9E52-9FB5-415C-A09C-BB68FDEECBDC}" uniqueName="20" name="Afdeling" queryTableFieldId="20" dataDxfId="24"/>
-    <tableColumn id="21" xr3:uid="{695E3E88-9634-46FC-ACB8-11F49E458C94}" uniqueName="21" name="Projectleider" queryTableFieldId="21" dataDxfId="23"/>
-    <tableColumn id="22" xr3:uid="{40800C44-E907-4858-9480-1D613D69FD66}" uniqueName="22" name="Opdrachtgever" queryTableFieldId="22" dataDxfId="22"/>
-    <tableColumn id="23" xr3:uid="{860959CB-7913-4355-B863-A764DB83CDD0}" uniqueName="23" name="Prioriteit" queryTableFieldId="23" dataDxfId="21"/>
-    <tableColumn id="24" xr3:uid="{817E512B-CCEF-4AA4-A43E-727AE552BF37}" uniqueName="24" name="Status" queryTableFieldId="24" dataDxfId="20"/>
-    <tableColumn id="25" xr3:uid="{0E32CE31-BA04-40BC-AACF-A27111980187}" uniqueName="25" name="Startdatum" queryTableFieldId="25" dataDxfId="19"/>
-    <tableColumn id="26" xr3:uid="{51DFA4C1-1FBB-4B30-80AD-83EA699A08D2}" uniqueName="26" name="Einddatum_gepland" queryTableFieldId="26" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{0253E53A-40A2-4DC8-A9DD-E43E7FA56125}" uniqueName="17" name="Project_ID" queryTableFieldId="17" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{CC51713D-8C64-4013-8757-A5457F2FE0D9}" uniqueName="18" name="Projectnaam" queryTableFieldId="18" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{A1C2B82E-44B8-4820-A84A-0772B352AB67}" uniqueName="19" name="Categorie" queryTableFieldId="19" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{BDAC9E52-9FB5-415C-A09C-BB68FDEECBDC}" uniqueName="20" name="Afdeling" queryTableFieldId="20" dataDxfId="11"/>
+    <tableColumn id="21" xr3:uid="{695E3E88-9634-46FC-ACB8-11F49E458C94}" uniqueName="21" name="Projectleider" queryTableFieldId="21" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{40800C44-E907-4858-9480-1D613D69FD66}" uniqueName="22" name="Opdrachtgever" queryTableFieldId="22" dataDxfId="9"/>
+    <tableColumn id="23" xr3:uid="{860959CB-7913-4355-B863-A764DB83CDD0}" uniqueName="23" name="Prioriteit" queryTableFieldId="23" dataDxfId="8"/>
+    <tableColumn id="24" xr3:uid="{817E512B-CCEF-4AA4-A43E-727AE552BF37}" uniqueName="24" name="Status" queryTableFieldId="24" dataDxfId="7"/>
+    <tableColumn id="25" xr3:uid="{0E32CE31-BA04-40BC-AACF-A27111980187}" uniqueName="25" name="Startdatum" queryTableFieldId="25" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{51DFA4C1-1FBB-4B30-80AD-83EA699A08D2}" uniqueName="26" name="Einddatum_gepland" queryTableFieldId="26" dataDxfId="5"/>
     <tableColumn id="27" xr3:uid="{4071721A-8AC3-4759-9777-78D3DB85BF00}" uniqueName="27" name="Einddatum_werkelijk" queryTableFieldId="27"/>
-    <tableColumn id="28" xr3:uid="{A14EB393-22D2-41B5-AAAA-1644591BEBF8}" uniqueName="28" name="Voortgang_pct" queryTableFieldId="28" dataDxfId="17"/>
-    <tableColumn id="29" xr3:uid="{69240D3B-1B4C-43E3-BDDD-B7AC9C94B763}" uniqueName="29" name="Budget_EUR" queryTableFieldId="29" dataDxfId="16"/>
-    <tableColumn id="30" xr3:uid="{431A1335-744E-4332-B85D-1D12F08F2F11}" uniqueName="30" name="Kosten_EUR" queryTableFieldId="30" dataDxfId="15"/>
-    <tableColumn id="31" xr3:uid="{3AEF5743-4E87-4F42-B1FD-F6387F782FC4}" uniqueName="31" name="Risico" queryTableFieldId="31" dataDxfId="14"/>
-    <tableColumn id="32" xr3:uid="{C3CD2FB6-7D42-41F7-BDA8-54296D9F008B}" uniqueName="32" name="Regio" queryTableFieldId="32" dataDxfId="13"/>
+    <tableColumn id="28" xr3:uid="{A14EB393-22D2-41B5-AAAA-1644591BEBF8}" uniqueName="28" name="Voortgang_pct" queryTableFieldId="28" dataDxfId="4"/>
+    <tableColumn id="29" xr3:uid="{69240D3B-1B4C-43E3-BDDD-B7AC9C94B763}" uniqueName="29" name="Budget_EUR" queryTableFieldId="29" dataDxfId="3"/>
+    <tableColumn id="30" xr3:uid="{431A1335-744E-4332-B85D-1D12F08F2F11}" uniqueName="30" name="Kosten_EUR" queryTableFieldId="30" dataDxfId="2"/>
+    <tableColumn id="31" xr3:uid="{3AEF5743-4E87-4F42-B1FD-F6387F782FC4}" uniqueName="31" name="Risico" queryTableFieldId="31" dataDxfId="1"/>
+    <tableColumn id="32" xr3:uid="{C3CD2FB6-7D42-41F7-BDA8-54296D9F008B}" uniqueName="32" name="Regio" queryTableFieldId="32" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1840,14 +1846,14 @@
       <c r="F22" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="23">
-        <v>27092026</v>
+      <c r="G22" s="29" t="s">
+        <v>54</v>
       </c>
       <c r="H22" s="23"/>
       <c r="I22" s="23"/>
       <c r="J22" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="J22" ca="1">IF(_xlfn.CONCAT(cfg_sources[[#This Row],[Bestandslocatie]:[REGEX vervangen met]])="","-",DATA.SOURCE($B22,$C22,$D22,$E22,$F22,$G22,$H22,$I22))</f>
-        <v>C:\Users\sgoos\Documents\demo_projects-27092026.xlsx</v>
+        <v>C:\Users\sgoos\Documents\demo_projects-27-09-2026.xlsx</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
